--- a/data/trans_orig/IQ11_1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ11_1-Clase-trans_orig.xlsx
@@ -1069,7 +1069,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8751</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21075</t>
+          <t>21754</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>27,22%</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10592</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8885</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13440</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3278</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7326</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5181,12 +5181,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>27975</t>
+          <t>27948</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>33132</t>
+          <t>32524</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>39967</t>
+          <t>39895</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>62768</t>
+          <t>63105</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>71233</t>
+          <t>71239</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3556</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10172</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4876</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6744,12 +6744,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -6785,12 +6785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13745</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7457,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -7942,12 +7942,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1343</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -8018,12 +8018,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8088,12 +8088,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13739</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18613</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21633</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>30770</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8710,7 +8710,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,86%</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8801,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>11991</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8816,12 +8816,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15233</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>22517</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -9291,7 +9291,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>38,12%</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>704</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>54,56%</t>
         </is>
       </c>
     </row>
@@ -9508,12 +9508,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9523,12 +9523,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -9817,7 +9817,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5634</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -9923,12 +9923,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9958,12 +9958,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9973,12 +9973,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17685</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10008,12 +10008,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10084,12 +10084,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -10145,12 +10145,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>26152</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>36181</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>42630</t>
+          <t>42624</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>53298</t>
+          <t>53245</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10195,12 +10195,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>71658</t>
+          <t>71306</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>87449</t>
+          <t>87156</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10230,12 +10230,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11030,7 +11030,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,41%</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2484</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12809,7 +12809,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>591</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13041,12 +13041,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13102,12 +13102,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13117,12 +13117,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13137,12 +13137,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12517</t>
+          <t>12674</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13152,12 +13152,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5452</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -13809,7 +13809,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>11838</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -14755,7 +14755,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14805,7 +14805,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14825,7 +14825,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14840,7 +14840,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4335</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -14977,7 +14977,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15022,12 +15022,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15057,12 +15057,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>17810</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -15118,12 +15118,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>37481</t>
+          <t>37549</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15133,12 +15133,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15153,12 +15153,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>50817</t>
+          <t>50442</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>58452</t>
+          <t>58543</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16605,7 +16605,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16625,7 +16625,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -16696,7 +16696,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -17788,7 +17788,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -17803,7 +17803,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -17949,7 +17949,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17969,7 +17969,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -17984,7 +17984,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -18040,7 +18040,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -18075,7 +18075,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -18090,7 +18090,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -19243,7 +19243,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19258,7 +19258,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19313,7 +19313,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -19349,7 +19349,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -19364,7 +19364,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -19419,7 +19419,7 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>537</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
@@ -19434,7 +19434,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19889,7 +19889,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -19930,7 +19930,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -19945,12 +19945,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -19960,12 +19960,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -19980,12 +19980,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -19995,7 +19995,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -20021,7 +20021,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -20056,12 +20056,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15427</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23407</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20071,12 +20071,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20091,12 +20091,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39565</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20106,12 +20106,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
